--- a/database/ipcdb rev02.xlsx
+++ b/database/ipcdb rev02.xlsx
@@ -9,11 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16092" windowHeight="10512"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16092" windowHeight="10512" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="json example" sheetId="2" r:id="rId2"/>
+    <sheet name="Data Dict" sheetId="4" r:id="rId2"/>
+    <sheet name="Menu" sheetId="8" r:id="rId3"/>
+    <sheet name="Script" sheetId="7" r:id="rId4"/>
+    <sheet name="คำขอ AI" sheetId="6" r:id="rId5"/>
+    <sheet name="json example" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="429">
   <si>
     <t>suppliers</t>
   </si>
@@ -33,15 +37,6 @@
     <t>location</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>inspect_header</t>
-  </si>
-  <si>
-    <t>inspect_detail</t>
-  </si>
-  <si>
     <t>supplier_name</t>
   </si>
   <si>
@@ -67,9 +62,6 @@
   </si>
   <si>
     <t>retention_value</t>
-  </si>
-  <si>
-    <t>inspect_no</t>
   </si>
   <si>
     <t>period</t>
@@ -271,9 +263,6 @@
     <t>ชื่อผู้รับเหมา</t>
   </si>
   <si>
-    <t>รหัสสถานที่</t>
-  </si>
-  <si>
     <t>ชื่อสถานที่</t>
   </si>
   <si>
@@ -281,9 +270,6 @@
   </si>
   <si>
     <t>รหัสแผนก</t>
-  </si>
-  <si>
-    <t>เลขที่ PO</t>
   </si>
   <si>
     <t>ชื่อโครงการ</t>
@@ -478,94 +464,13 @@
     <t>contract_value - total_value_interim_payment (ยอดเงินงวดคงเหลือ)</t>
   </si>
   <si>
-    <t>status_plan</t>
-  </si>
-  <si>
-    <t>inspector</t>
-  </si>
-  <si>
-    <t>ผู้ตรวจสอบ</t>
-  </si>
-  <si>
-    <t>วันที่ตรวจสอบ</t>
-  </si>
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>ตำแหน่ง</t>
-  </si>
-  <si>
     <t>หมายเหตุ</t>
   </si>
   <si>
-    <t>approver1</t>
-  </si>
-  <si>
-    <t>approve_date1</t>
-  </si>
-  <si>
-    <t>วันที่อนุมัติ 1</t>
-  </si>
-  <si>
-    <t>ผู้อนุมัติ 1</t>
-  </si>
-  <si>
-    <t>approver2</t>
-  </si>
-  <si>
-    <t>ผู้อนุมัติ 2</t>
-  </si>
-  <si>
-    <t>approve_date2</t>
-  </si>
-  <si>
-    <t>วันที่อนุมัติ 2</t>
-  </si>
-  <si>
-    <t>approver3</t>
-  </si>
-  <si>
-    <t>ผู้อนุมัติ 3</t>
-  </si>
-  <si>
-    <t>approve_date3</t>
-  </si>
-  <si>
-    <t>วันที่อนุมัติ 3</t>
-  </si>
-  <si>
-    <t>approver4</t>
-  </si>
-  <si>
-    <t>ผู้อนุมัติ 4</t>
-  </si>
-  <si>
-    <t>approve_date4</t>
-  </si>
-  <si>
-    <t>วันที่อนุมัติ 4</t>
-  </si>
-  <si>
-    <t>approver5</t>
-  </si>
-  <si>
-    <t>approve_date5</t>
-  </si>
-  <si>
-    <t>ผู้อนุมัติ 5</t>
-  </si>
-  <si>
-    <t>วันที่อนุมัติ 5</t>
-  </si>
-  <si>
     <t>create_by</t>
   </si>
   <si>
     <t>create_date</t>
-  </si>
-  <si>
-    <t>inspect_date</t>
   </si>
   <si>
     <t>ผู้จัดทำเอกสาร</t>
@@ -603,10 +508,6 @@
     <t>total_retention_value</t>
   </si>
   <si>
-    <t>{"1":{"detail":"งานเดินท่อร้อยสายวางระบบโคมไฟ LED","remark":"(งวดที่1) เบิก 30%ของงานติดตั้ง"},
-"2":{"detail":"งานติดตั้งโคมไฟ LED","remark":""}}</t>
-  </si>
-  <si>
     <t>working_name_th</t>
   </si>
   <si>
@@ -628,12 +529,6 @@
     <t>เงินมัดจำ(%)</t>
   </si>
   <si>
-    <t>project_no</t>
-  </si>
-  <si>
-    <t>รหัสโครงการ</t>
-  </si>
-  <si>
     <t>project</t>
   </si>
   <si>
@@ -643,9 +538,6 @@
     <t>ชื่อแผนก</t>
   </si>
   <si>
-    <t>department</t>
-  </si>
-  <si>
     <t>password</t>
   </si>
   <si>
@@ -653,18 +545,6 @@
   </si>
   <si>
     <t>username</t>
-  </si>
-  <si>
-    <t>suppliers_no</t>
-  </si>
-  <si>
-    <t>รหัสผู้รับเหมา(auto generate)</t>
-  </si>
-  <si>
-    <t>location_no</t>
-  </si>
-  <si>
-    <t>department_no</t>
   </si>
   <si>
     <t>deposit_percent</t>
@@ -707,19 +587,10 @@
     <t>มูลค่าตามงาน PO</t>
   </si>
   <si>
-    <t>รหัสการตรวจรับงาน(Auto Increment)</t>
-  </si>
-  <si>
     <t>จำนวนวันดำเนินการรวม(working_date_from - working_date_to + 1)</t>
   </si>
   <si>
     <t>inspect_period</t>
-  </si>
-  <si>
-    <t>งวด</t>
-  </si>
-  <si>
-    <t>งวด(Auto Increment)</t>
   </si>
   <si>
     <t>workload_planned_percent</t>
@@ -829,18 +700,6 @@
     <t>ยอดเบิกเงินงวดสะสม(%)</t>
   </si>
   <si>
-    <t>มี retention(true/false)</t>
-  </si>
-  <si>
-    <t>มีการเบิกจ่าย(true/false)</t>
-  </si>
-  <si>
-    <t>อาจสร้าง table เพื่อเก็บข้อมูลแทน</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>ลำดับรายการ Auto Increment</t>
   </si>
   <si>
@@ -850,14 +709,1028 @@
     <t>รายละเอียด</t>
   </si>
   <si>
-    <t>inspect_workflow</t>
+    <t>inspect_main</t>
+  </si>
+  <si>
+    <t>inspect_period_detail</t>
+  </si>
+  <si>
+    <t>สถานะเอกสาร</t>
+  </si>
+  <si>
+    <t>inspect_status</t>
+  </si>
+  <si>
+    <t>plan_status</t>
+  </si>
+  <si>
+    <t>มีการเบิกจ่ายหรือไม่(true/false)</t>
+  </si>
+  <si>
+    <t>มี retention หรือไม่(true/false)</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>level_id</t>
+  </si>
+  <si>
+    <t>approver_id</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>approval_status</t>
+  </si>
+  <si>
+    <t>approval_date</t>
+  </si>
+  <si>
+    <t>department_id</t>
+  </si>
+  <si>
+    <t>รหัสแผนก(ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>users</t>
+  </si>
+  <si>
+    <t>departments</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>รหัสผู้รับเหมา(ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>suppliers_id</t>
+  </si>
+  <si>
+    <t>รหัสสถานที่(ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>location_id</t>
+  </si>
+  <si>
+    <t>รหัสโครงการ(ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>po_id</t>
+  </si>
+  <si>
+    <t>รหัส PO (ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>ผู้สร้าง PO (เชื่อมโยงกับตาราง Users)</t>
+  </si>
+  <si>
+    <t>ชื่อ-นามสกุล</t>
+  </si>
+  <si>
+    <t>บทบาทของผู้ใช้งาน (เช่น "ผู้ขอซื้อ", "ผู้จัดการ", "ผู้อำนวยการ")</t>
+  </si>
+  <si>
+    <t>approval_workflow</t>
+  </si>
+  <si>
+    <t>approval_levels</t>
+  </si>
+  <si>
+    <t>กำหนดระดับการอนุมัติในแต่ละ Workflow</t>
+  </si>
+  <si>
+    <t>บันทึกการอนุมัติ PO ในแต่ละระดับ</t>
+  </si>
+  <si>
+    <t>รหัส Workflow (ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>workflow_name</t>
+  </si>
+  <si>
+    <t>workflow_id</t>
+  </si>
+  <si>
+    <t>รหัสระดับ (ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>รหัส Workflow (เชื่อมโยงกับตาราง Approval Workflow)</t>
+  </si>
+  <si>
+    <t>ลำดับของระดับการอนุมัติ (เช่น 1, 2, 3)</t>
+  </si>
+  <si>
+    <t>บทบาทของผู้มีสิทธิ์อนุมัติ (เช่น "ผู้จัดการ", "ผู้อำนวยการ")</t>
+  </si>
+  <si>
+    <t>level_order</t>
+  </si>
+  <si>
+    <t>approver_role</t>
+  </si>
+  <si>
+    <t>รหัสการอนุมัติ (ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>approval_id</t>
+  </si>
+  <si>
+    <t>สถานะการอนุมัติ ("อนุมัติ", "ไม่อนุมัติ", "รออนุมัติ")</t>
+  </si>
+  <si>
+    <t>วันที่และเวลาที่อนุมัติ</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>inspect_id</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจรับงาน (ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>รหัส PO</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจรับงาน(เชื่อมโยงกับตาราง inspect_period)</t>
+  </si>
+  <si>
+    <t>งวด(เชื่อมโยงกับตาราง inspect_period)</t>
+  </si>
+  <si>
+    <t>รหัสระดับ (เชื่อมโยงกับตาราง approval_levels)</t>
+  </si>
+  <si>
+    <t>รหัสผู้ทำการอนุมัติ (เชื่อมโยงกับตาราง users)</t>
+  </si>
+  <si>
+    <t>inspect_approvals</t>
+  </si>
+  <si>
+    <t>รออนุมัติ</t>
+  </si>
+  <si>
+    <t>อนุมัติ</t>
+  </si>
+  <si>
+    <t>ผู้จัดการ</t>
+  </si>
+  <si>
+    <t>ผู้อำนวยการ</t>
+  </si>
+  <si>
+    <t>ความคิดเห็น (TEXT)</t>
+  </si>
+  <si>
+    <t>กรรมการผู้จัดการ</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>******</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>Mo Salah</t>
+  </si>
+  <si>
+    <t>mosalah</t>
+  </si>
+  <si>
+    <t>Arne Slot</t>
+  </si>
+  <si>
+    <t>as007</t>
+  </si>
+  <si>
+    <t>ผู้ช่วยผู้จัดการ</t>
+  </si>
+  <si>
+    <t>John Henry</t>
+  </si>
+  <si>
+    <t>henry001</t>
+  </si>
+  <si>
+    <t>กำหนดขั้นตอนการอนุมัติ(ไม่จำเป็น)</t>
+  </si>
+  <si>
+    <t>ชื่อ Workflow (เช่น "การอนุมัติ Inspect ทั่วไป", "การอนุมัติ Inspect แบบพิเศษ")</t>
+  </si>
+  <si>
+    <t>การอนุมัติ Inspect ทั่วไป</t>
+  </si>
+  <si>
+    <t>การอนุมัติ Inspect พิเศษ</t>
+  </si>
+  <si>
+    <t>ไม่อนุมัติ</t>
+  </si>
+  <si>
+    <t>bosspaul</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>คำอธิบายเพิ่มเติม:
+การอนุมัติแบบเรียงลำดับจะถูกควบคุมโดย level_order ในตาราง approval_levels และ approval_status ในตาราง inspect_approvals
+เมื่อ inspect_period ถูกสร้างขึ้น จะมีการสร้าง record ในตาราง inspect_approvals 
+โดยมีจำนวน record ตามจำนวนรายการใน approval_levels ที่เลือก พร้อมสถานะจะถูกตั้งเป็น "รออนุมัติ" ทุก record
+เมื่อผู้มีสิทธิ์อนุมัติในระดับนั้นอนุมัติ สถานะการอนุมัติจะเปลี่ยนเป็น "อนุมัติ" และบันทึกการอนุมัติในระดับถัดไป
+กระบวนการนี้จะดำเนินไปจนถึงระดับสุดท้าย หากมีการไม่อนุมัติในระดับใดระดับหนึ่ง สถานะ Inspect จะเปลี่ยนเป็น "ไม่อนุมัติ"
+การใช้ approver_role ใน approval_levels ช่วยให้กำหนดผู้มีสิทธิ์อนุมัติได้ง่ายโดยไม่ต้องระบุผู้ใช้โดยตรง ทำให้ยืดหยุ่นกว่า</t>
+  </si>
+  <si>
+    <t>รหัส Workflow</t>
+  </si>
+  <si>
+    <t>current_status</t>
+  </si>
+  <si>
+    <t>current_level</t>
+  </si>
+  <si>
+    <t>สถานะปัจจุบันของคำขอ (เช่น รอดำเนินการ, อนุมัติ, ไม่อนุมัติ)</t>
+  </si>
+  <si>
+    <t>ระดับการอนุมัติปัจจุบัน</t>
+  </si>
+  <si>
+    <t>approval_status_id</t>
+  </si>
+  <si>
+    <t>approval_status_name</t>
+  </si>
+  <si>
+    <t>รหัสสถานะการอนุมัติ (ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>inspect_period_id</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจรับงวดงาน</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจรับงวดงาน(ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>งวด(ลำดับอัตโนมัติ 1, 2, 3, ...)</t>
+  </si>
+  <si>
+    <t>รหัสผู้ใช้งาน(ลำดับอัตโนมัติหรือกำหนดเอง)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>{"1":{"detail":"งานเดินท่อร้อยสายวางระบบโคมไฟ LED","remark":"(งวดที่1) เบิก 30%ของงานติดตั้ง"},
+"2":{"detail":"งานติดตั้งโคมไฟ LED","remark":""}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>***สร้างเป็นตาราง inspect_period_detail เพื่อเก็บข้อมูลแทน</t>
+    </r>
+  </si>
+  <si>
+    <t>inspect_period_detail_id</t>
+  </si>
+  <si>
+    <t>รหัสรายละเอียดการตรวจรับงวดงาน(ลำดับอัตโนมัติ)</t>
+  </si>
+  <si>
+    <t>order_no</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>INT (PK, AI)</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>รหัสสถานที่ (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>รหัสโครงการ (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>รหัส PO (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>เลขที่ PO</t>
+  </si>
+  <si>
+    <t>INT (FK)</t>
+  </si>
+  <si>
+    <t>รหัสโครงการ (Foreign Key อ้างอิงตาราง project)</t>
+  </si>
+  <si>
+    <t>รหัสสถานที่ (Foreign Key อ้างอิงตาราง location)</t>
+  </si>
+  <si>
+    <t>ชื่องาน (ภาษาไทย)</t>
+  </si>
+  <si>
+    <t>ชื่องาน (ภาษาอังกฤษ)</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>DECIMAL(15,2)</t>
+  </si>
+  <si>
+    <t>DECIMAL(5,2)</t>
+  </si>
+  <si>
+    <t>มูลค่าเงินมัดจำ</t>
+  </si>
+  <si>
+    <t>ผู้สร้าง PO (Foreign Key อ้างอิงตาราง users)</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>วันที่สร้าง PO</t>
+  </si>
+  <si>
+    <t>รหัส PO (Foreign Key อ้างอิงตาราง po)</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของเงินจ่ายระหว่างงวด</t>
+  </si>
+  <si>
+    <t>ตาราง: suppliers</t>
+  </si>
+  <si>
+    <t>ตาราง: location</t>
+  </si>
+  <si>
+    <t>ตาราง: project</t>
+  </si>
+  <si>
+    <t>ตาราง: po (Purchase Order)</t>
+  </si>
+  <si>
+    <t>รวม VAT หรือไม่ (เช่น 1 = รวม, 0 = ไม่รวม)</t>
+  </si>
+  <si>
+    <t>มูลค่าสัญญา (รวม VAT)</t>
+  </si>
+  <si>
+    <t>มีการวางเงินมัดจำหรือไม่ (เช่น 1 = มี, 0 = ไม่มี)</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์เงินมัดจำ</t>
+  </si>
+  <si>
+    <t>ตาราง: departments</t>
+  </si>
+  <si>
+    <t>รหัสแผนก (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>ตาราง: approval_status</t>
+  </si>
+  <si>
+    <t>รหัสสถานะการอนุมัติ (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>ชื่อสถานะการอนุมัติ (เช่น รออนุมัติ, อนุมัติแล้ว, ไม่อนุมัติ)</t>
+  </si>
+  <si>
+    <t>ตาราง: users</t>
+  </si>
+  <si>
+    <t>รหัสผ่าน (ควรเข้ารหัส)</t>
+  </si>
+  <si>
+    <t>บทบาท (เช่น ผู้บริหาร, พนักงานจัดซื้อ, ผู้อนุมัติ)</t>
+  </si>
+  <si>
+    <t>รหัสแผนก (Foreign Key อ้างอิงตาราง departments)</t>
+  </si>
+  <si>
+    <t>ตาราง: approval_workflow</t>
+  </si>
+  <si>
+    <t>รหัส Workflow (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>ตาราง: approval_levels</t>
+  </si>
+  <si>
+    <t>รหัส Level (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>รหัส Workflow (Foreign Key อ้างอิงตาราง approval_workflow)</t>
+  </si>
+  <si>
+    <t>ลำดับ Level ใน Workflow (เช่น 1, 2, 3) เพื่อกำหนดลำดับการอนุมัติจากน้อยไปมาก</t>
+  </si>
+  <si>
+    <t>บทบาทของผู้มีสิทธิ์อนุมัติ (เช่น Manager, Finance Director) หรือ User_ID ก็ได้</t>
+  </si>
+  <si>
+    <t>ตาราง: inspect_approvals</t>
+  </si>
+  <si>
+    <t>รหัสการอนุมัติ (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>รหัส Level (Foreign Key อ้างอิงตาราง approval_levels)</t>
+  </si>
+  <si>
+    <t>รหัสผู้อนุมัติ (Foreign Key อ้างอิงตาราง users)</t>
+  </si>
+  <si>
+    <t>รหัสสถานะการอนุมัติ (Foreign Key อ้างอิงตาราง approval_status)</t>
+  </si>
+  <si>
+    <t>วันที่อนุมัติ</t>
+  </si>
+  <si>
+    <t>Field Name</t>
+  </si>
+  <si>
+    <t>BOOLEAN/TINYINT</t>
+  </si>
+  <si>
+    <t>DATETIME/TIMESTAMP</t>
+  </si>
+  <si>
+    <t>สถานะการตรวจรับ (เช่น "รอตรวจ", "ตรวจแล้ว", "ผ่าน", "ไม่ผ่าน")</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจรับ (Foreign Key อ้างอิงตาราง inspect_main)</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของปริมาณงานที่วางแผนไว้</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของปริมาณงานที่ทำเสร็จจริง</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของปริมาณงานที่เหลือ</t>
+  </si>
+  <si>
+    <t>ระบุว่าจ่ายเงินแล้วหรือไม่ (เช่น 1=จ่ายแล้ว, 0=ยังไม่จ่าย)</t>
+  </si>
+  <si>
+    <t>ระบุว่าเป็นเงินประกันผลงานหรือไม่ (เช่น 1=ใช่, 0=ไม่ใช่)</t>
+  </si>
+  <si>
+    <t>รหัส Workflow (Foreign Key อ้างอิงตาราง workflows)</t>
+  </si>
+  <si>
+    <t>รหัสงวดการตรวจรับ (Foreign Key อ้างอิงตาราง inspect_period)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตาราง: inspect_main </t>
+  </si>
+  <si>
+    <t>ตาราง: inspect_period</t>
+  </si>
+  <si>
+    <t>ตาราง: inspect_period_detail</t>
+  </si>
+  <si>
+    <t>ขอ datadict ของตาราง โดยมีชื่อตารางและฟิลด์ตามนี้</t>
+  </si>
+  <si>
+    <t>รหัสผู้รับเหมา (Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>รหัสผู้รับเหมา (Foreign Key อ้างอิงตาราง suppliers)</t>
+  </si>
+  <si>
+    <t>มูลค่าสัญญาก่อน VAT
+ถ้าเลือกรวม vat จะได้ contract_value = contract_value - vat
+ถ้าเลือกไม่รวม vat จะได้ contract_value = contract_value</t>
+  </si>
+  <si>
+    <t>มูลค่า VAT
+ถ้าเลือกรวม vat จะได้ vat = contract_value *(7 /107)
+ถ้าเลือกไม่รวม vat จะได้ vat = contract_value * (7 /100)</t>
+  </si>
+  <si>
+    <t>รหัสผู้ใช้งาน (Primary Key, Auto Increment หรือกำหนดเอง)</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจสอบ (Foreign Key อ้างอิงตาราง inspect_period)</t>
+  </si>
+  <si>
+    <t>งวดการตรวจสอบ (เช่น งวดที่ 1, 2, 3)(เชื่อมโยงกับตาราง inspect_period)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ความคิดเห็น </t>
+  </si>
+  <si>
+    <t>ยอดเงินงวดคงเหลือ(contract_value - total_value_interim_payment)</t>
+  </si>
+  <si>
+    <t>มูลค่าเงินประกันผลงานทั้งหมด(Total Value of Retension)</t>
+  </si>
+  <si>
+    <t>ผู้จัดทำเอกสาร (Foreign Key อ้างอิงตาราง users)</t>
+  </si>
+  <si>
+    <t>รหัสการตรวจรับงาน(Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>รหัสงวดการตรวจรับ(Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>ลำดับงวด(ลำดับอัตโนมัติ 1, 2, 3, ...)</t>
+  </si>
+  <si>
+    <t>เงินจ่ายระหว่างงวด(ยอดเบิกเงินงวดปัจจุบัน/ ยอดเบิกเงินงวดสุดท้าย(Net Value of Current Claim))</t>
+  </si>
+  <si>
+    <t>ยอดเบิกเงินงวดสะสมถึงปัจจุบัน(ไม่รวมปัจจุบัน)(Less Previous Interim Payment)</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของยอดเบิกเงินงวดสะสมถึงปัจจุบัน(ไม่รวมปัจจุบัน)</t>
+  </si>
+  <si>
+    <t>ยอดเบิกเงินงวดสะสม(interim_payment + interim_payment_less_previous(Total Value Of Interim Payment))</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของยอดเบิกเงินงวดสะสม</t>
+  </si>
+  <si>
+    <t>ยอดเงินงวดคงเหลือ(contract_value - interim_payment_accumulated)</t>
+  </si>
+  <si>
+    <t>เปอร์เซ็นต์ของยอดเงินงวดคงเหลือ</t>
+  </si>
+  <si>
+    <t>เงินประกันผลงานงวดนี้(Less Retension)</t>
+  </si>
+  <si>
+    <t>สถานะปัจจุบันของ Workflow (เช่น รอดำเนินการ, อนุมัติ, ไม่อนุมัติ)</t>
+  </si>
+  <si>
+    <t>ระดับการอนุมัติปัจจุบันของ Workflow</t>
+  </si>
+  <si>
+    <t>รหัสรายละเอียดงวดการตรวจรับงวดงาน(Primary Key, Auto Increment)</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง suppliers</t>
+  </si>
+  <si>
+    <t>CREATE TABLE suppliers (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    suppliers_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    supplier_name VARCHAR(255) NOT NULL</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง location</t>
+  </si>
+  <si>
+    <t>CREATE TABLE location (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    location_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    location_name VARCHAR(255) NOT NULL</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง project</t>
+  </si>
+  <si>
+    <t>CREATE TABLE project (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    project_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    project_name VARCHAR(255) NOT NULL</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง po</t>
+  </si>
+  <si>
+    <t>CREATE TABLE po (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    po_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    po_no VARCHAR(50) UNIQUE NOT NULL, -- เพิ่ม UNIQUE เพื่อป้องกันเลข PO ซ้ำ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    project_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    suppliers_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    location_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    working_name_th VARCHAR(255),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    working_name_en VARCHAR(255),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    is_include_vat BOOLEAN DEFAULT TRUE, -- กำหนดค่าเริ่มต้นเป็น TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    contract_value DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    contract_value_before DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    vat DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    is_deposit BOOLEAN DEFAULT FALSE, -- กำหนดค่าเริ่มต้นเป็น FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    deposit_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    deposit_value DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    create_by INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    create_date DATETIME DEFAULT CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง inspect_main</t>
+  </si>
+  <si>
+    <t>CREATE TABLE inspect_main (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inspect_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    po_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    working_date_from DATE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    working_date_to DATE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    working_day INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    remain_value_interim_payment DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    total_retention_value DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inspect_status VARCHAR(50), -- ควรใช้ ENUM หรือตาราง lookup สำหรับสถานะ</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง inspect_period</t>
+  </si>
+  <si>
+    <t>CREATE TABLE inspect_period (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inspect_period_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inspect_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    period INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    workload_planned_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    workload_actual_completed_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    workload_remaining_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_less_previous DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_less_previous_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_accumulated DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_accumulated_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_remain DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    interim_payment_remain_percent DECIMAL(5, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    retention_value DECIMAL(15, 2),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    plan_status VARCHAR(50), -- ควรใช้ ENUM หรือตาราง lookup สำหรับสถานะ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    is_paid BOOLEAN DEFAULT FALSE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    is_retention BOOLEAN DEFAULT FALSE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    remark VARCHAR(255),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    workflow_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    current_status VARCHAR(50), -- ควรใช้ ENUM หรือตาราง lookup สำหรับสถานะ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    current_level INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    list_json JSON -- ใช้ JSON type สำหรับเก็บข้อมูล JSON</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง inspect_period_detail</t>
+  </si>
+  <si>
+    <t>CREATE TABLE inspect_period_detail (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inspect_period_detail_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inspect_period_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    order_no INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    details VARCHAR(255),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    remark VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง departments</t>
+  </si>
+  <si>
+    <t>CREATE TABLE departments (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    department_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    department_name VARCHAR(255) NOT NULL</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง approval_status</t>
+  </si>
+  <si>
+    <t>CREATE TABLE approval_status (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approval_status_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approval_status_name VARCHAR(255) NOT NULL</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง users</t>
+  </si>
+  <si>
+    <t>CREATE TABLE users (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    username VARCHAR(50) UNIQUE NOT NULL, -- เพิ่ม UNIQUE เพื่อป้องกัน username ซ้ำ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    password VARCHAR(255) NOT NULL, -- ควรเก็บ password แบบ hash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    full_name VARCHAR(255),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    role VARCHAR(50),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    department_id INT</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง approval_workflow</t>
+  </si>
+  <si>
+    <t>CREATE TABLE approval_workflow (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    workflow_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    workflow_name VARCHAR(255) NOT NULL</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง approval_levels</t>
+  </si>
+  <si>
+    <t>CREATE TABLE approval_levels (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    level_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    level_order INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approver_role VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>-- สร้างตาราง inspect_approvals</t>
+  </si>
+  <si>
+    <t>CREATE TABLE inspect_approvals (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approval_id INT PRIMARY KEY AUTO_INCREMENT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    level_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approver_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approval_status_id INT,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    approval_date DATETIME DEFAULT CURRENT_TIMESTAMP,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    comments VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>คำอธิบายและข้อควรระวัง:</t>
+  </si>
+  <si>
+    <t>Primary Key (PK): ถูกกำหนดให้ทุกตารางด้วย AUTO_INCREMENT เพื่อให้ MySQL สร้าง ID อัตโนมัติ</t>
+  </si>
+  <si>
+    <t>Foreign Key (FK): ใช้เพื่อเชื่อมโยงตารางต่างๆ และบังคับความสัมพันธ์ (Referential Integrity) เช่น po.project_id อ้างอิงไปยัง project.project_id</t>
+  </si>
+  <si>
+    <t>Data Types: เลือกประเภทข้อมูลให้เหมาะสม เช่น VARCHAR สำหรับข้อความ, INT สำหรับจำนวนเต็ม, DECIMAL สำหรับทศนิยม, DATE สำหรับวันที่, DATETIME สำหรับวันที่และเวลา, BOOLEAN สำหรับค่าความจริง (true/false), JSON สำหรับข้อมูล JSON</t>
+  </si>
+  <si>
+    <t>NOT NULL: กำหนดให้ฟิลด์ที่ไม่ควรมีค่าว่าง</t>
+  </si>
+  <si>
+    <t>UNIQUE: ใช้เพื่อป้องกันค่าซ้ำ เช่น po_no และ username</t>
+  </si>
+  <si>
+    <t>DEFAULT: กำหนดค่าเริ่มต้น เช่น is_include_vat เป็น TRUE และ create_date เป็น CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Password: ควรเก็บรหัสผ่านในรูปแบบ hash เช่น SHA256 เพื่อความปลอดภัย ไม่ควรเก็บเป็น plain VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>Enum/Lookup Table: สำหรับฟิลด์ inspect_status, plan_status, current_status ควรพิจารณาใช้ ENUM type หรือสร้างตาราง lookup เพื่อเก็บค่าสถานะ เพื่อความถูกต้องและง่ายต่อการจัดการ</t>
+  </si>
+  <si>
+    <t>Decimal Precision: DECIMAL(15, 2) หมายถึง เลขทศนิยมที่มีความแม่นยำ 15 หลัก โดยมี 2 หลักเป็นทศนิยม ปรับได้ตามความเหมาะสม</t>
+  </si>
+  <si>
+    <t>JSON Type: ใช้ JSON type ใน MySQL 5.7+ เพื่อเก็บข้อมูล JSON อย่างมีประสิทธิภาพ</t>
+  </si>
+  <si>
+    <t>Foreign Key บนตาราง po และ inspect_main: ได้เพิ่ม Foreign Key ไปยังตาราง users ในฟิลด์ create_by เพื่อบันทึกว่าใครเป็นผู้สร้างข้อมูล</t>
+  </si>
+  <si>
+    <t>Foreign Key บนตาราง inspect_period: ได้เพิ่ม Foreign Key ไปยังตาราง approval_workflow ในฟิลด์ workflow_id</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Workflow</t>
+  </si>
+  <si>
+    <t>ข้อมูลผู้ใช้</t>
+  </si>
+  <si>
+    <t>ขั้นตอนการอนุมัติ</t>
+  </si>
+  <si>
+    <t>ตาราง role</t>
+  </si>
+  <si>
+    <t>ตาราง department</t>
+  </si>
+  <si>
+    <t>ตาราง users</t>
+  </si>
+  <si>
+    <t>Inspection</t>
+  </si>
+  <si>
+    <t>ตาราง inspect_status</t>
+  </si>
+  <si>
+    <t>ตาราง plan_status</t>
+  </si>
+  <si>
+    <t>&gt;&gt;ตาราง: inspect_period, ตาราง: inspect_period_details</t>
+  </si>
+  <si>
+    <t>การตรวจรับงาน</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -936,8 +1809,34 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -950,8 +1849,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FFEF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEDE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -959,11 +1876,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -993,6 +1925,87 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1002,6 +2015,10 @@
   <colors>
     <mruColors>
       <color rgb="FF0000FF"/>
+      <color rgb="FFFFEDE7"/>
+      <color rgb="FFF7FFEF"/>
+      <color rgb="FFE5FFFF"/>
+      <color rgb="FFE7FECE"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1278,707 +2295,1341 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="130" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="10.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="B19" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C14" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>116</v>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>36</v>
-      </c>
+      <c r="B43" s="5"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>10</v>
+      <c r="A44" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>46</v>
+      <c r="B46" s="10" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>84</v>
+      <c r="A47" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G63" s="15"/>
+    </row>
+    <row r="64" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G64" s="15"/>
+    </row>
+    <row r="65" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G65" s="15"/>
+    </row>
+    <row r="66" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A66" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68" s="5"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75" s="5"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="5"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C81" s="19">
+        <v>1</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C82" s="19">
+        <v>2</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C83" s="19">
+        <v>3</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B84" s="5"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G85" s="20" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="H85" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" s="19">
+        <v>1001</v>
+      </c>
+      <c r="D86" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="H86" s="19"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C87" s="19">
+        <v>1002</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G87" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="H87" s="19"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C88" s="19">
+        <v>1003</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="G88" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="H88" s="19"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C89" s="19">
+        <v>1004</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G89" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H89" s="19"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="19">
+        <v>1005</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G90" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="H90" s="19"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="C93" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D93" s="25" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="6" t="s">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C94" s="19">
+        <v>1</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="11"/>
+      <c r="C95" s="19">
+        <v>2</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="13" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="B96" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D97" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="E97" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="F97" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C98" s="23">
+        <v>1</v>
+      </c>
+      <c r="D98" s="19">
+        <v>1</v>
+      </c>
+      <c r="E98" s="23">
+        <v>1</v>
+      </c>
+      <c r="F98" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C99" s="23">
+        <v>2</v>
+      </c>
+      <c r="D99" s="19">
+        <v>1</v>
+      </c>
+      <c r="E99" s="23">
+        <v>2</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C100" s="19">
+        <v>3</v>
+      </c>
+      <c r="D100" s="19">
+        <v>1</v>
+      </c>
+      <c r="E100" s="19">
+        <v>3</v>
+      </c>
+      <c r="F100" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="G100" s="3"/>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="11"/>
+      <c r="C101" s="19">
+        <v>4</v>
+      </c>
+      <c r="D101" s="19">
+        <v>2</v>
+      </c>
+      <c r="E101" s="19">
+        <v>3</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="G101" s="3"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="11"/>
+      <c r="C102" s="19">
+        <v>5</v>
+      </c>
+      <c r="D102" s="19">
+        <v>2</v>
+      </c>
+      <c r="E102" s="19">
+        <v>4</v>
+      </c>
+      <c r="F102" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G102" s="3"/>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="6" t="s">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" s="6" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="C104" s="22" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
+      <c r="D104" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E104" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="G104" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H104" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I104" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J104" s="22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="29">
+        <v>1</v>
+      </c>
+      <c r="D105" s="29">
+        <v>1</v>
+      </c>
+      <c r="E105" s="29">
+        <v>1</v>
+      </c>
+      <c r="F105" s="29">
+        <v>1</v>
+      </c>
+      <c r="G105" s="29">
+        <v>1002</v>
+      </c>
+      <c r="H105" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="I105" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="J105" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C106" s="29">
+        <v>2</v>
+      </c>
+      <c r="D106" s="29">
+        <v>1</v>
+      </c>
+      <c r="E106" s="29">
+        <v>1</v>
+      </c>
+      <c r="F106" s="29">
+        <v>2</v>
+      </c>
+      <c r="G106" s="29">
+        <v>1003</v>
+      </c>
+      <c r="H106" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="I106" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="J106" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C107" s="29">
+        <v>3</v>
+      </c>
+      <c r="D107" s="29">
+        <v>1</v>
+      </c>
+      <c r="E107" s="29">
+        <v>1</v>
+      </c>
+      <c r="F107" s="29">
+        <v>3</v>
+      </c>
+      <c r="G107" s="29">
+        <v>1004</v>
+      </c>
+      <c r="H107" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="I107" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="J107" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C108" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
+      <c r="D108" s="26">
+        <v>1</v>
+      </c>
+      <c r="E108" s="26">
+        <v>2</v>
+      </c>
+      <c r="F108" s="26">
+        <v>1</v>
+      </c>
+      <c r="G108" s="26">
+        <v>1002</v>
+      </c>
+      <c r="H108" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="I108" s="28">
+        <v>45500.625</v>
+      </c>
+      <c r="J108" s="27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="C109" s="26">
+        <v>5</v>
+      </c>
+      <c r="D109" s="26">
+        <v>1</v>
+      </c>
+      <c r="E109" s="26">
+        <v>2</v>
+      </c>
+      <c r="F109" s="26">
+        <v>2</v>
+      </c>
+      <c r="G109" s="26">
+        <v>1003</v>
+      </c>
+      <c r="H109" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="I109" s="28">
+        <v>45500.645833333336</v>
+      </c>
+      <c r="J109" s="27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="C110" s="26">
+        <v>6</v>
+      </c>
+      <c r="D110" s="26">
+        <v>1</v>
+      </c>
+      <c r="E110" s="26">
+        <v>2</v>
+      </c>
+      <c r="F110" s="26">
+        <v>3</v>
+      </c>
+      <c r="G110" s="26">
+        <v>1004</v>
+      </c>
+      <c r="H110" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="I110" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="J110" s="27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B90" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" s="10" t="s">
-        <v>121</v>
+      <c r="B111" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C111" s="31">
+        <v>7</v>
+      </c>
+      <c r="D111" s="31">
+        <v>2</v>
+      </c>
+      <c r="E111" s="31">
+        <v>1</v>
+      </c>
+      <c r="F111" s="32">
+        <v>4</v>
+      </c>
+      <c r="G111" s="32">
+        <v>1004</v>
+      </c>
+      <c r="H111" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="I111" s="34">
+        <v>45500.625</v>
+      </c>
+      <c r="J111" s="33" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C112" s="31">
+        <v>8</v>
+      </c>
+      <c r="D112" s="31">
+        <v>2</v>
+      </c>
+      <c r="E112" s="31">
+        <v>1</v>
+      </c>
+      <c r="F112" s="32">
+        <v>5</v>
+      </c>
+      <c r="G112" s="32">
+        <v>1005</v>
+      </c>
+      <c r="H112" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="I112" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="J112" s="33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="B113" s="39"/>
+      <c r="C113" s="23"/>
+      <c r="D113" s="23"/>
+      <c r="E113" s="23"/>
+      <c r="F113" s="23"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="22"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="22"/>
+    </row>
+    <row r="114" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="39"/>
+      <c r="B114" s="39"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+    </row>
+    <row r="115" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="39"/>
+      <c r="B115" s="39"/>
+      <c r="G115" s="18"/>
+    </row>
+    <row r="116" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="39"/>
+      <c r="B116" s="39"/>
+      <c r="G116" s="18"/>
+    </row>
+    <row r="117" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="39"/>
+      <c r="B117" s="39"/>
+      <c r="G117" s="18"/>
+    </row>
+    <row r="118" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="39"/>
+      <c r="B118" s="39"/>
+      <c r="G118" s="18"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C119" s="17"/>
+      <c r="D119" s="17"/>
+      <c r="E119" s="17"/>
+      <c r="F119" s="17"/>
+      <c r="G119" s="18"/>
+      <c r="H119" s="17"/>
+      <c r="I119" s="17"/>
+      <c r="J119" s="17"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C120" s="17"/>
+      <c r="D120" s="17"/>
+      <c r="E120" s="17"/>
+      <c r="F120" s="17"/>
+      <c r="G120" s="18"/>
+      <c r="H120" s="17"/>
+      <c r="I120" s="17"/>
+      <c r="J120" s="17"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A113:B118"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1986,57 +3637,2615 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:C125"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="28.88671875" style="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.88671875" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="43"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A1" s="41" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A2" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A3" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A4" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A6" s="41" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A7" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A8" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A9" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A11" s="41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A12" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A13" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A14" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A16" s="41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A17" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A18" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A19" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A20" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A21" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A22" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A23" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A24" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A25" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A26" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="63" x14ac:dyDescent="0.6">
+      <c r="A27" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="63" x14ac:dyDescent="0.6">
+      <c r="A28" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A29" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A30" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A31" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A32" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A33" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A35" s="41" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A36" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A37" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A38" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A40" s="41" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A41" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A42" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="45" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A43" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A45" s="41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A46" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A47" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A48" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A49" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="45" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A50" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C50" s="45" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A51" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" s="45" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A52" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A54" s="41" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A55" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A56" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C56" s="45" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A57" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="45" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A59" s="41" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A60" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B60" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A61" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="45" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A62" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" s="45" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A63" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C63" s="45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A64" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C64" s="45" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A66" s="41" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A67" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A68" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C68" s="45" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A69" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" s="45" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A70" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" s="45" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A71" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71" s="45" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A72" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C72" s="45" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A73" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C73" s="45" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A74" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="C74" s="45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A75" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B75" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C75" s="45" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A77" s="41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A78" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A79" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C79" s="45" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A80" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A81" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C81" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A82" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C82" s="45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A83" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C83" s="45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A84" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" s="45" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A85" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B85" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C85" s="45" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A86" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="45" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A87" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B87" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C87" s="45" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="42" x14ac:dyDescent="0.6">
+      <c r="A88" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B88" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="C88" s="45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A90" s="41" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A91" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="B91" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C91" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A92" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="B92" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C92" s="45" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A93" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B93" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C93" s="45" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A94" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" s="45" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A95" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C95" s="45" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="42" x14ac:dyDescent="0.6">
+      <c r="A96" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B96" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C96" s="45" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A97" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B97" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C97" s="45" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A98" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B98" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C98" s="45" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A99" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C99" s="45" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A100" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B100" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C100" s="45" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="42" x14ac:dyDescent="0.6">
+      <c r="A101" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="B101" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C101" s="45" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="42" x14ac:dyDescent="0.6">
+      <c r="A102" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B102" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C102" s="45" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="42" x14ac:dyDescent="0.6">
+      <c r="A103" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B103" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="45" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A104" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B104" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C104" s="45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A105" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B105" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C105" s="45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A106" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B106" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C106" s="45" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A107" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C107" s="45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A108" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="C108" s="45" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A109" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B109" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="C109" s="45" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A110" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B110" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C110" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A111" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="B111" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C111" s="45" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A112" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B112" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112" s="45" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A113" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="B113" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C113" s="45" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A115" s="41" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A116" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C116" s="44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A117" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B117" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C117" s="45" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A118" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="B118" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C118" s="45" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A119" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B119" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="C119" s="45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A120" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B120" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C120" s="45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A121" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B121" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C121" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.6"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="51.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="40" t="s">
+        <v>424</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>269</v>
+      </c>
+      <c r="B20" t="s">
+        <v>427</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A149"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="179" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A2" s="37" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A3" s="37" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A4" s="37" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A6" s="37"/>
+    </row>
+    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A8" s="37" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A9" s="37" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A11" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A12" s="37"/>
+    </row>
+    <row r="13" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A13" s="37" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A14" s="37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A15" s="37" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A16" s="37" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A18" s="37"/>
+    </row>
+    <row r="19" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A19" s="37" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A20" s="37" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A21" s="37" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A22" s="37" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A23" s="37" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A24" s="37" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A25" s="37" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A26" s="37" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A27" s="37" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A28" s="37" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A29" s="37" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A30" s="37" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A31" s="37" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A32" s="37" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A33" s="37" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A34" s="37" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A35" s="37" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A36" s="37" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A37" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A38" s="37"/>
+    </row>
+    <row r="39" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A39" s="37" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A40" s="37" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A41" s="37" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A42" s="37" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A43" s="37" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A44" s="37" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A45" s="37" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A46" s="37" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A47" s="37" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A48" s="37" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A49" s="37" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A50" s="37" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A51" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A52" s="37"/>
+    </row>
+    <row r="53" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A53" s="37" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A54" s="37" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A55" s="37" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A56" s="37" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A57" s="37" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A58" s="37" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A59" s="37" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A60" s="37" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A61" s="37" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A62" s="37" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A63" s="37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A64" s="37" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A65" s="37" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A66" s="37" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A67" s="37" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A68" s="37" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A69" s="37" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A70" s="37" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A71" s="37" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A72" s="37" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A73" s="37" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A74" s="37" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A75" s="37" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A76" s="37" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A77" s="37" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A78" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A79" s="37"/>
+    </row>
+    <row r="80" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A80" s="37" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A81" s="37" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A82" s="37" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A83" s="37" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A84" s="37" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A85" s="37" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A86" s="37" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A87" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A88" s="37"/>
+    </row>
+    <row r="89" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A89" s="37" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A90" s="37" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A91" s="37" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A92" s="37" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A93" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A94" s="37"/>
+    </row>
+    <row r="95" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A95" s="37" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A96" s="37" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A97" s="37" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A98" s="37" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A99" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A100" s="37"/>
+    </row>
+    <row r="101" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A101" s="37" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A102" s="37" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A103" s="37" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A104" s="37" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A105" s="37" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A106" s="37" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A107" s="37" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A108" s="37" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A109" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A110" s="37"/>
+    </row>
+    <row r="111" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A111" s="37" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A112" s="37" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A113" s="37" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A114" s="37" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A115" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A116" s="37"/>
+    </row>
+    <row r="117" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A117" s="37" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A118" s="37" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A119" s="37" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A120" s="37" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A121" s="37" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A122" s="37" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A123" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A124" s="37"/>
+    </row>
+    <row r="125" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A125" s="37" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A126" s="37" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A127" s="37" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A128" s="37" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A129" s="37" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A130" s="37" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A131" s="37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A132" s="37" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A133" s="37" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A134" s="37" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A135" s="37" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A136" s="37"/>
+    </row>
+    <row r="137" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A137" s="37" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A138" s="37" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A139" s="37" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A140" s="37" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A141" s="37" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A142" s="37" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A143" s="37" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A144" s="37" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A145" s="37" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A146" s="37" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A147" s="37" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A148" s="37" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A149" s="37" t="s">
+        <v>416</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A123"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="45.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
